--- a/AI Audit Log_LeVanDai.xlsx
+++ b/AI Audit Log_LeVanDai.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/917556b196d2d829/Desktop/SWP391/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/917556b196d2d829/Desktop/SWP391/ai-audit-log-LeVanDaiDE290256/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3DB4BAFD-22E4-4A56-8BB6-7291655F4E02}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5950629-F5CD-4841-899A-7C510DA2CE26}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{3DB4BAFD-22E4-4A56-8BB6-7291655F4E02}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B235EA-87AC-46D3-A6AE-A62F1F58E06B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>STT</t>
   </si>
@@ -118,6 +118,25 @@
   <si>
     <t>AI Response
  (Summary)</t>
+  </si>
+  <si>
+    <t>PROBLEM-SOLVING</t>
+  </si>
+  <si>
+    <t>Pattern Recognition / Abstraction</t>
+  </si>
+  <si>
+    <t>Đề xuất actor phù hợp cho hệ thống spa nhiều chi nhánh và phân chia quyền hạn.</t>
+  </si>
+  <si>
+    <t>AI giúp phân quyền rõ ràng hơn so với hệ thống cũ. Tôi chỉnh sửa lại để Branch Manager chỉ quản lý dữ liệu thuộc chi nhánh của mình thay vì toàn hệ thống. Điều này giúp mô hình phân quyền thực tế hơn.</t>
+  </si>
+  <si>
+    <t>AI đề xuất các actor gồm Owner, Branch Manager, Staff, Customer và Guest cùng các use case tương ứng.</t>
+  </si>
+  <si>
+    <t>Thiết kế actor và use case cho
+ hệ thống nhiều chi nhánh.</t>
   </si>
 </sst>
 </file>
@@ -190,31 +209,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.1640625" customWidth="1"/>
@@ -562,80 +584,129 @@
     <col min="7" max="7" width="55.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="56">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" ht="56">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="55.5" customHeight="1">
+    <row r="2" spans="1:10" ht="55.5" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="8" t="s">
-        <v>5</v>
-      </c>
+      <c r="B2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:7" ht="55" customHeight="1">
+    <row r="3" spans="1:10" ht="55" customHeight="1">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="8" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9" t="s">
         <v>5</v>
       </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:7" ht="56">
+    <row r="4" spans="1:10" ht="56">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9" t="s">
         <v>5</v>
       </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:7" ht="56">
+    <row r="5" spans="1:10" ht="56">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9" t="s">
         <v>5</v>
       </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AI Audit Log_LeVanDai.xlsx
+++ b/AI Audit Log_LeVanDai.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/917556b196d2d829/Desktop/SWP391/ai-audit-log-LeVanDaiDE290256/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{3DB4BAFD-22E4-4A56-8BB6-7291655F4E02}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B235EA-87AC-46D3-A6AE-A62F1F58E06B}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{ED16BCF0-CF13-415F-AF1E-AE119F2C1B37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{03581079-8C5A-4FAC-8377-B0BA12F6C992}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Week 2" sheetId="4" r:id="rId2"/>
+    <sheet name="Assignment 1" sheetId="2" r:id="rId3"/>
+    <sheet name="Assignment 2" sheetId="3" r:id="rId4"/>
+    <sheet name="Assignment 3" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>STT</t>
   </si>
@@ -138,12 +139,102 @@
     <t>Thiết kế actor và use case cho
  hệ thống nhiều chi nhánh.</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <r>
+      <t>Prompt Type
+ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DECISION / PROBLEM-SOLVING / VERIFICATION</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Giai đoạn/Thành phần DTC
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decomposition, Pattern Recognition, Abstraction, 
+Algorithms, Research stage</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Problem/Context
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Summary)</t>
+    </r>
+  </si>
+  <si>
+    <t>Architecture / Data Modeling (Thiết kế Kiến trúc/Dữ liệu)</t>
+  </si>
+  <si>
+    <t>Sau khi chốt 35 Use Cases, nhóm cần thiết kế cấu trúc cơ sở dữ liệu (Database Schema) để đảm bảo lưu trữ được dữ liệu của nhiều chi nhánh mà không bị xung đột hay lặp dữ liệu.</t>
+  </si>
+  <si>
+    <t>"Dựa trên 35 Use Cases quản lý spa nhiều chi nhánh đã chốt, hãy thiết kế các bảng database (ERD) bằng SQL. Cần làm rõ mối quan hệ giữa bảng Branches, Staff, Bookings và Inventory để không bị lộ dữ liệu giữa các cơ sở."</t>
+  </si>
+  <si>
+    <t>AI cung cấp cấu trúc các bảng SQL cốt lõi kèm theo các ràng buộc khóa ngoại (FOREIGN KEY). Giải thích chi tiết cách dùng branch_id ở các bảng để phân quyền dữ liệu và cách thiết kế bảng trung gian để quản lý các buổi lẻ trong một gói liệu trình.</t>
+  </si>
+  <si>
+    <t>Delta: Định hình được cấu trúc Database chuẩn cho mô hình Chuỗi (Multi-branch). Biết cách tách biệt bảng Services (danh mục chung) và Branch_Services (giá hoặc trạng thái riêng tại từng cơ sở).Reflection: Thấy được tầm quan trọng của việc chuẩn hóa dữ liệu (Database Normalization) để tránh dư thừa và đảm bảo tính toàn vẹn dữ liệu khi có hàng ngàn lượt đặt lịch cùng lúc</t>
+  </si>
+  <si>
+    <t>System Design
+ (Thiết kế hệ thống - ERD Diagram)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +264,35 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -182,7 +302,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -205,11 +325,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -237,6 +394,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.1640625" customWidth="1"/>
@@ -708,6 +895,11 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
     </row>
+    <row r="11" spans="1:10">
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -715,6 +907,80 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+    </row>
+    <row r="2" spans="1:12" ht="143.5" customHeight="1">
+      <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -723,7 +989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -732,8 +998,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0A2B67-D23B-4DD4-996A-E5076823F00F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>

--- a/AI Audit Log_LeVanDai.xlsx
+++ b/AI Audit Log_LeVanDai.xlsx
@@ -8,18 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/917556b196d2d829/Desktop/SWP391/ai-audit-log-LeVanDaiDE290256/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{ED16BCF0-CF13-415F-AF1E-AE119F2C1B37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{03581079-8C5A-4FAC-8377-B0BA12F6C992}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{ED16BCF0-CF13-415F-AF1E-AE119F2C1B37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{366DEB31-9DE2-4905-853F-2670B722DBCA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="4" r:id="rId2"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId3"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId4"/>
-    <sheet name="Assignment 3" sheetId="6" r:id="rId5"/>
+    <sheet name="Week 3" sheetId="8" r:id="rId3"/>
+    <sheet name="Week 4" sheetId="9" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="10" r:id="rId5"/>
+    <sheet name="Week 6" sheetId="11" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="12" r:id="rId7"/>
+    <sheet name="Week 8" sheetId="13" r:id="rId8"/>
+    <sheet name="Week 9" sheetId="14" r:id="rId9"/>
+    <sheet name="Week 10" sheetId="15" r:id="rId10"/>
+    <sheet name="Assignment 1" sheetId="2" r:id="rId11"/>
+    <sheet name="Assignment 2" sheetId="3" r:id="rId12"/>
+    <sheet name="Assignment 3" sheetId="6" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="83">
   <si>
     <t>STT</t>
   </si>
@@ -95,12 +103,6 @@
     <t>Human Delta &amp; Reflection</t>
   </si>
   <si>
-    <t xml:space="preserve">• Critical Thinking: AI đúng/sai ở đâu? Phát hiện hallucination? 
-• Contextualization: Bối cảnh thực tế mà AI không biết? 
-• Creative Synthesis: Tôi đã thay đổi/kết hợp/tối ưu như thế nào? 
-• Decision Ownership: Quyết định cuối cùng và lý do? </t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Problem/Context
 </t>
@@ -211,23 +213,202 @@
     </r>
   </si>
   <si>
-    <t>Architecture / Data Modeling (Thiết kế Kiến trúc/Dữ liệu)</t>
-  </si>
-  <si>
-    <t>Sau khi chốt 35 Use Cases, nhóm cần thiết kế cấu trúc cơ sở dữ liệu (Database Schema) để đảm bảo lưu trữ được dữ liệu của nhiều chi nhánh mà không bị xung đột hay lặp dữ liệu.</t>
-  </si>
-  <si>
-    <t>"Dựa trên 35 Use Cases quản lý spa nhiều chi nhánh đã chốt, hãy thiết kế các bảng database (ERD) bằng SQL. Cần làm rõ mối quan hệ giữa bảng Branches, Staff, Bookings và Inventory để không bị lộ dữ liệu giữa các cơ sở."</t>
-  </si>
-  <si>
-    <t>AI cung cấp cấu trúc các bảng SQL cốt lõi kèm theo các ràng buộc khóa ngoại (FOREIGN KEY). Giải thích chi tiết cách dùng branch_id ở các bảng để phân quyền dữ liệu và cách thiết kế bảng trung gian để quản lý các buổi lẻ trong một gói liệu trình.</t>
-  </si>
-  <si>
-    <t>Delta: Định hình được cấu trúc Database chuẩn cho mô hình Chuỗi (Multi-branch). Biết cách tách biệt bảng Services (danh mục chung) và Branch_Services (giá hoặc trạng thái riêng tại từng cơ sở).Reflection: Thấy được tầm quan trọng của việc chuẩn hóa dữ liệu (Database Normalization) để tránh dư thừa và đảm bảo tính toàn vẹn dữ liệu khi có hàng ngàn lượt đặt lịch cùng lúc</t>
-  </si>
-  <si>
-    <t>System Design
- (Thiết kế hệ thống - ERD Diagram)</t>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>Research Stage / Decomposition</t>
+  </si>
+  <si>
+    <t>Xác định phạm vi đề tài từ hệ thống spa 1 chi nhánh sang hệ thống spa đa chi nhánh.</t>
+  </si>
+  <si>
+    <t>Hãy phân tích sự khác nhau giữa hệ thống spa một chi nhánh và multi-branch spa management system, đồng thời đề xuất các chức năng quan trọng.</t>
+  </si>
+  <si>
+    <t>AI đề xuất bổ sung branch management, booking theo chi nhánh, chuyển lịch giữa các chi nhánh và dashboard doanh thu.</t>
+  </si>
+  <si>
+    <t>AI tập trung đúng vào business logic thay vì CRUD cơ bản. Tuy nhiên tôi loại bỏ các chức năng quá lớn như AI recommendation và payment online để phù hợp thời gian thực hiện. Tôi quyết định xây dựng hệ thống Multi-Branch Spa Management System với trọng tâm là booking và quản lý nhiều chi nhánh.</t>
+  </si>
+  <si>
+    <t>VERIFICATION</t>
+  </si>
+  <si>
+    <t>Algorithms / Research Stage</t>
+  </si>
+  <si>
+    <t>Kiểm tra tính khả thi của tính năng gợi ý chi nhánh thay thế khi cơ sở hiện tại full slot.</t>
+  </si>
+  <si>
+    <t>Nếu chi nhánh khách hàng chọn đã hết lịch, hệ thống nên đề xuất chi nhánh khác như thế nào?</t>
+  </si>
+  <si>
+    <t>AI đề xuất sử dụng khoảng cách địa lý kết hợp số lượng slot còn trống để xếp hạng các chi nhánh phù hợp.</t>
+  </si>
+  <si>
+    <t>AI đúng ở phần ranking theo khoảng cách nhưng chưa xét trường hợp chi nhánh gần nhất cũng hết slot. Tôi bổ sung thêm tiêu chí thời gian trống gần nhất để tối ưu trải nghiệm khách hàng. Cuối cùng tôi chọn mô hình hybrid ranking dựa trên khoảng cách và available slot làm business logic chính của dự án.</t>
+  </si>
+  <si>
+    <t>Algorithms / Abstraction</t>
+  </si>
+  <si>
+    <t>Thiết kế quy trình booking cho khách hàng trong hệ thống spa đa chi nhánh.</t>
+  </si>
+  <si>
+    <t>Hãy đề xuất booking flow phù hợp cho hệ thống spa nhiều chi nhánh.</t>
+  </si>
+  <si>
+    <t>AI đề xuất flow gồm: chọn dịch vụ → chọn chi nhánh → kiểm tra slot → xác nhận booking → gửi thông báo xác nhận.</t>
+  </si>
+  <si>
+    <t>AI đưa ra flow cơ bản nhưng chưa tận dụng lợi thế multi-branch. Tôi bổ sung bước tìm chi nhánh phù hợp trước khi booking và thêm cơ chế suggest branch khi chi nhánh hiện tại full slot. Điều này giúp tăng khả năng khách hàng hoàn thành booking thay vì hủy bỏ.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition / Algorithms</t>
+  </si>
+  <si>
+    <t>Thiết kế cơ chế quản lý slot booking cho từng chi nhánh.</t>
+  </si>
+  <si>
+    <t>Hệ thống nên quản lý slot booking theo cách nào để tránh overbooking?</t>
+  </si>
+  <si>
+    <t>AI đề xuất mỗi booking gắn với một time slot và hệ thống kiểm tra slot trước khi tạo lịch hẹn.</t>
+  </si>
+  <si>
+    <t>AI đúng về nguyên tắc nhưng chưa xử lý trường hợp nhiều nhân viên cùng phục vụ trong một khung giờ. Tôi bổ sung BookingSlot riêng biệt và giới hạn số lượng booking theo năng lực phục vụ của từng chi nhánh. Quyết định này giúp hệ thống linh hoạt hơn khi mở rộng quy mô.</t>
+  </si>
+  <si>
+    <t>Algorithms</t>
+  </si>
+  <si>
+    <t>Kiểm tra tính hợp lý của tính năng chuyển lịch giữa các chi nhánh.</t>
+  </si>
+  <si>
+    <t>Khi khách hàng muốn chuyển booking sang chi nhánh khác thì hệ thống cần xử lý những gì?</t>
+  </si>
+  <si>
+    <t>AI đề xuất kiểm tra slot còn trống, nhân viên khả dụng và cập nhật branch mới cho booking.</t>
+  </si>
+  <si>
+    <t>AI chưa xét đến xung đột lịch làm việc của nhân viên. Tôi bổ sung bước kiểm tra employee schedule và chỉ cho phép chuyển booking khi toàn bộ điều kiện hợp lệ. Đây là nghiệp vụ quan trọng vì là tính năng đặc trưng của Aura Spa.</t>
+  </si>
+  <si>
+    <t>Xây dựng thuật toán gợi ý chi nhánh thay thế khi cơ sở hiện tại hết lịch.</t>
+  </si>
+  <si>
+    <t>Hãy đề xuất thuật toán phù hợp để suggest chi nhánh khác cho khách hàng.</t>
+  </si>
+  <si>
+    <t>AI đề xuất sắp xếp các chi nhánh theo khoảng cách địa lý và số lượng slot còn trống.</t>
+  </si>
+  <si>
+    <t>AI tập trung vào khoảng cách nhưng chưa xét đến nhu cầu thực tế của khách hàng. Tôi bổ sung tiêu chí thời gian trống gần nhất và tạo thuật toán hybrid ranking gồm khoảng cách + available slot + thời gian phù hợp. Tôi quyết định chọn đây là business logic trọng tâm của hệ thống Aura Spa vì tạo sự khác biệt so với các hệ thống booking thông thường.</t>
+  </si>
+  <si>
+    <t>Abstraction / Research Stage</t>
+  </si>
+  <si>
+    <t>Thiết kế các thực thể chính cho hệ thống Aura Spa đa chi nhánh.</t>
+  </si>
+  <si>
+    <t>Hãy đề xuất các entity cần thiết cho hệ thống spa nhiều chi nhánh.</t>
+  </si>
+  <si>
+    <t>AI đề xuất các bảng Users, Branches, Services, Employees, Bookings, Reviews và Payments.</t>
+  </si>
+  <si>
+    <t>AI xác định đúng các entity cốt lõi nhưng chưa thể hiện rõ đặc thù multi-branch. Tôi bổ sung branch_id vào nhiều thực thể và thêm BranchManager để phản ánh cơ cấu quản lý thực tế. Điều này giúp mô hình dữ liệu phù hợp hơn với yêu cầu dự án.</t>
+  </si>
+  <si>
+    <t>Decomposition / Abstraction</t>
+  </si>
+  <si>
+    <t>Thiết kế mối quan hệ giữa Booking và các thành phần liên quan.</t>
+  </si>
+  <si>
+    <t>Booking nên liên kết với những thực thể nào trong hệ thống?</t>
+  </si>
+  <si>
+    <t>AI đề xuất liên kết Booking với Customer, Service, Branch và Employee.</t>
+  </si>
+  <si>
+    <t>AI đưa ra cấu trúc cơ bản nhưng chưa hỗ trợ tốt việc quản lý slot. Tôi bổ sung BookingSlot làm thực thể trung gian để dễ xử lý đổi lịch, chuyển chi nhánh và kiểm soát overbooking. Đây là quyết định quan trọng cho các chức năng booking nâng cao.</t>
+  </si>
+  <si>
+    <t>Kiểm tra tính hợp lý của mô hình nhân viên trong hệ thống đa chi nhánh.</t>
+  </si>
+  <si>
+    <t>Nhân viên nên thuộc nhiều chi nhánh hay chỉ một chi nhánh trong hệ thống spa?</t>
+  </si>
+  <si>
+    <t>AI đề xuất cho phép nhân viên làm việc ở nhiều chi nhánh để tăng tính linh hoạt.</t>
+  </si>
+  <si>
+    <t>AI đúng về mặt mở rộng nhưng chưa phù hợp với phạm vi SWP391. Tôi quyết định mỗi nhân viên chỉ thuộc một chi nhánh nhằm đơn giản hóa quản lý lịch làm việc và giảm độ phức tạp của dữ liệu. Đây là trade-off hợp lý cho giai đoạn hiện tại.</t>
+  </si>
+  <si>
+    <t>Thiết kế cấu trúc lưu trữ slot booking trong cơ sở dữ liệu.</t>
+  </si>
+  <si>
+    <t>Nên lưu slot trực tiếp trong Booking hay tách thành bảng riêng?</t>
+  </si>
+  <si>
+    <t>AI đề xuất lưu trực tiếp thời gian bắt đầu và kết thúc trong Booking để đơn giản hóa hệ thống.</t>
+  </si>
+  <si>
+    <t>AI đơn giản hóa quá mức và chưa xét đến nhu cầu quản lý slot động. Tôi tách BookingSlot thành bảng riêng để dễ dàng mở rộng, quản lý năng lực phục vụ của từng chi nhánh và hỗ trợ chức năng chuyển lịch trong tương lai. Đây là lựa chọn phù hợp hơn với định hướng multi-branch của Aura Spa.</t>
+  </si>
+  <si>
+    <t>Research Stage / Abstraction</t>
+  </si>
+  <si>
+    <t>Lựa chọn kiến trúc phù hợp cho hệ thống Aura Spa.</t>
+  </si>
+  <si>
+    <t>Với hệ thống spa đa chi nhánh, nên sử dụng Monolithic hay Microservices?</t>
+  </si>
+  <si>
+    <t>AI đề xuất Microservices để dễ mở rộng và quản lý nhiều module độc lập.</t>
+  </si>
+  <si>
+    <t>AI đúng về khả năng mở rộng nhưng chưa phù hợp với quy mô và thời gian thực hiện của SWP391. Tôi quyết định sử dụng kiến trúc Monolithic với các module tách biệt để giảm độ phức tạp nhưng vẫn đảm bảo khả năng bảo trì và phát triển sau này.</t>
+  </si>
+  <si>
+    <t>Thiết kế các module chính cho backend hệ thống.</t>
+  </si>
+  <si>
+    <t>Hãy đề xuất cấu trúc module backend cho hệ thống spa đa chi nhánh.</t>
+  </si>
+  <si>
+    <t>AI đề xuất các module gồm Authentication, Branch Management, Booking Management, Employee Management và Reporting.</t>
+  </si>
+  <si>
+    <t>AI đưa ra cấu trúc hợp lý nhưng chưa tách riêng Slot Management. Tôi bổ sung module BookingSlot để xử lý lịch hẹn và kiểm soát overbooking hiệu quả hơn. Điều này giúp business logic booking rõ ràng và dễ bảo trì.</t>
+  </si>
+  <si>
+    <t>Kiểm tra cách thiết kế API cho chức năng booking.</t>
+  </si>
+  <si>
+    <t>API tạo booking nên nhận những thông tin nào từ client?</t>
+  </si>
+  <si>
+    <t>AI đề xuất branchId, serviceId, customerId, employeeId và bookingTime.</t>
+  </si>
+  <si>
+    <t>AI chưa xét đến trường hợp khách hàng không chọn nhân viên cụ thể. Tôi điều chỉnh để employeeId là tùy chọn và hệ thống có thể tự động gán nhân viên phù hợp dựa trên lịch làm việc hiện có. Điều này phản ánh đúng nghiệp vụ thực tế của spa.</t>
+  </si>
+  <si>
+    <t>Thiết kế API cho tính năng gợi ý chi nhánh thay thế.</t>
+  </si>
+  <si>
+    <t>Nên xây dựng API suggest branch như thế nào khi chi nhánh hiện tại full slot?</t>
+  </si>
+  <si>
+    <t>AI đề xuất API nhận branchId và trả về danh sách các chi nhánh khác còn slot.</t>
+  </si>
+  <si>
+    <t>AI mới xét đến tình trạng slot mà chưa tính khoảng cách và thời gian phù hợp. Tôi mở rộng API để nhận thêm vị trí khách hàng và thời gian mong muốn, từ đó áp dụng thuật toán hybrid ranking nhằm đưa ra các đề xuất có giá trị hơn cho người dùng.</t>
   </si>
 </sst>
 </file>
@@ -302,7 +483,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -338,35 +519,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,9 +558,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -416,14 +570,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -759,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.1640625" customWidth="1"/>
@@ -782,13 +933,13 @@
         <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>4</v>
@@ -802,102 +953,79 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>11</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" ht="55" customHeight="1">
+    <row r="3" spans="1:10" ht="84">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="B3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="G3" s="9" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="56">
+    <row r="4" spans="1:10" ht="70">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="B4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="G4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" ht="56">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+        <v>28</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="E11" t="s">
-        <v>14</v>
+      <c r="E7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -906,9 +1034,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1:L2"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E016D57F-1E9A-46C6-A9D7-2EF9F505177F}">
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="31.4140625" customWidth="1"/>
@@ -916,71 +1044,135 @@
     <col min="4" max="4" width="44.1640625" customWidth="1"/>
     <col min="5" max="5" width="38.4140625" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
-    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="57.5" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="15" t="s">
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-    </row>
-    <row r="2" spans="1:12" ht="143.5" customHeight="1">
-      <c r="A2" s="12">
-        <v>1</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>18</v>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="56">
+      <c r="A2" s="16">
+        <v>8</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>17</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="56">
+      <c r="A3" s="16">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="16">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="C4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="70">
+      <c r="A5" s="16">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -989,7 +1181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14"/>
@@ -998,11 +1190,1115 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0A2B67-D23B-4DD4-996A-E5076823F00F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="70">
+      <c r="A2" s="17">
+        <v>4</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="70">
+      <c r="A3" s="17">
+        <v>5</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="17">
+        <v>6</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="84">
+      <c r="A5" s="17">
+        <v>7</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0484857C-4A21-4A6B-B466-F18AAC78F0ED}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="56">
+      <c r="A2" s="16">
+        <v>8</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="56">
+      <c r="A3" s="16">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="16">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="70">
+      <c r="A5" s="16">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC6560E-89F1-42E8-87A4-F335DF5D1C50}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="56">
+      <c r="A2" s="16">
+        <v>12</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="56">
+      <c r="A3" s="16">
+        <v>13</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="16">
+        <v>14</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="56">
+      <c r="A5" s="16">
+        <v>15</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29DC8F4C-1351-4FE4-8122-15F34B9A48D6}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="56">
+      <c r="A2" s="16">
+        <v>8</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="56">
+      <c r="A3" s="16">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="16">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="70">
+      <c r="A5" s="16">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFCC2499-BED8-4AA5-94CB-7C8751FC2540}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="56">
+      <c r="A2" s="16">
+        <v>8</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="56">
+      <c r="A3" s="16">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="16">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="70">
+      <c r="A5" s="16">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E18554F2-18D8-43A5-949D-1BC2080C9515}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="56">
+      <c r="A2" s="16">
+        <v>8</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="56">
+      <c r="A3" s="16">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="16">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="70">
+      <c r="A5" s="16">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A587915-313D-45B6-93D4-397D77ADF393}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="56">
+      <c r="A2" s="16">
+        <v>8</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="56">
+      <c r="A3" s="16">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="16">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="70">
+      <c r="A5" s="16">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{735CF029-11BF-4654-9E3E-B740C3374434}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.1640625" customWidth="1"/>
+    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="56">
+      <c r="A2" s="16">
+        <v>8</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="56">
+      <c r="A3" s="16">
+        <v>9</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="56">
+      <c r="A4" s="16">
+        <v>10</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="70">
+      <c r="A5" s="16">
+        <v>11</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AI Audit Log_LeVanDai.xlsx
+++ b/AI Audit Log_LeVanDai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/917556b196d2d829/Desktop/SWP391/ai-audit-log-LeVanDaiDE290256/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{ED16BCF0-CF13-415F-AF1E-AE119F2C1B37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{366DEB31-9DE2-4905-853F-2670B722DBCA}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{ED16BCF0-CF13-415F-AF1E-AE119F2C1B37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{30F8FB22-79E7-428E-ABEF-D084E9CEC40F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="9" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,6 @@
     <sheet name="Week 8" sheetId="13" r:id="rId8"/>
     <sheet name="Week 9" sheetId="14" r:id="rId9"/>
     <sheet name="Week 10" sheetId="15" r:id="rId10"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId11"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId12"/>
-    <sheet name="Assignment 3" sheetId="6" r:id="rId13"/>
   </sheets>
   <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="124">
   <si>
     <t>STT</t>
   </si>
@@ -410,12 +407,329 @@
   <si>
     <t>AI mới xét đến tình trạng slot mà chưa tính khoảng cách và thời gian phù hợp. Tôi mở rộng API để nhận thêm vị trí khách hàng và thời gian mong muốn, từ đó áp dụng thuật toán hybrid ranking nhằm đưa ra các đề xuất có giá trị hơn cho người dùng.</t>
   </si>
+  <si>
+    <t>Thiết kế mô hình phân quyền cho hệ thống Aura Spa.</t>
+  </si>
+  <si>
+    <t>Hãy đề xuất role và quyền hạn phù hợp cho hệ thống spa đa chi nhánh.</t>
+  </si>
+  <si>
+    <t>AI đề xuất các role gồm Owner, Manager, Staff và Customer với quyền truy cập khác nhau.</t>
+  </si>
+  <si>
+    <t>AI xác định đúng các role chính nhưng chưa phân biệt rõ Branch Manager và Owner. Tôi giới hạn Branch Manager chỉ được thao tác dữ liệu thuộc chi nhánh của mình, trong khi Owner có quyền xem và quản lý toàn bộ hệ thống. Điều này phù hợp hơn với mô hình vận hành thực tế của Aura Spa.</t>
+  </si>
+  <si>
+    <t>Lựa chọn phương thức xác thực cho hệ thống web.</t>
+  </si>
+  <si>
+    <t>Với ReactJS và NodeJS, nên sử dụng Session Authentication hay JWT Authentication?</t>
+  </si>
+  <si>
+    <t>AI đề xuất JWT Authentication vì phù hợp với REST API và frontend tách biệt.</t>
+  </si>
+  <si>
+    <t>AI đưa ra giải pháp phù hợp với kiến trúc dự án. Tôi quyết định sử dụng JWT kết hợp Refresh Token để tăng tính bảo mật và hỗ trợ đăng nhập trên nhiều thiết bị. Đây là hướng triển khai phù hợp cho hệ thống hiện đại.</t>
+  </si>
+  <si>
+    <t>Algorithms / Security</t>
+  </si>
+  <si>
+    <t>Kiểm tra cách bảo vệ API theo role.</t>
+  </si>
+  <si>
+    <t>Làm thế nào để ngăn Staff truy cập các API dành cho Owner?</t>
+  </si>
+  <si>
+    <t>AI đề xuất middleware kiểm tra role sau khi xác thực JWT.</t>
+  </si>
+  <si>
+    <t>AI đúng về mặt kỹ thuật nhưng chưa đề cập đến kiểm tra branch ownership. Tôi bổ sung thêm bước xác thực branchId đối với Branch Manager để đảm bảo người quản lý chỉ thao tác trên dữ liệu thuộc phạm vi được cấp quyền. Điều này giúp tăng tính an toàn và đúng nghiệp vụ.</t>
+  </si>
+  <si>
+    <t>Security / Research Stage</t>
+  </si>
+  <si>
+    <t>Thiết kế quy trình đăng ký và quản lý tài khoản khách hàng.</t>
+  </si>
+  <si>
+    <t>Hệ thống spa nên cho phép khách hàng đăng ký tài khoản như thế nào?</t>
+  </si>
+  <si>
+    <t>AI đề xuất đăng ký bằng email và mật khẩu, kết hợp xác thực email.</t>
+  </si>
+  <si>
+    <t>AI đưa ra giải pháp tiêu chuẩn nhưng có thể làm tăng thời gian onboarding. Tôi quyết định hỗ trợ cả đăng ký bằng Google OAuth bên cạnh email/password để cải thiện trải nghiệm người dùng và giảm tỷ lệ bỏ đăng ký giữa chừng.</t>
+  </si>
+  <si>
+    <t>Prompt Type</t>
+  </si>
+  <si>
+    <t>Giai đoạn/Thành phần DTC</t>
+  </si>
+  <si>
+    <t>Problem/Context</t>
+  </si>
+  <si>
+    <t>AI Response</t>
+  </si>
+  <si>
+    <t>Khách hàng đặt lịch hẹn tại AuraSpa cần thanh toán đặt cọc trực tuyến qua cổng VNPAY để giữ chỗ.</t>
+  </si>
+  <si>
+    <t>"Viết hàm khởi tạo URL thanh toán VNPAY (createPaymentUrl) trong NestJS nhận vào amount, orderInfo, và returnUrl, thực hiện hash mã SHA512 theo tài liệu kỹ thuật VNPAY v2.1.0."</t>
+  </si>
+  <si>
+    <t>AI cung cấp đoạn code cấu hình hàm băm HMAC-SHA512 và tạo chuỗi query string sắp xếp theo thứ tự alphabet chuẩn quy định của VNPAY.</t>
+  </si>
+  <si>
+    <r>
+      <t>Đồng ý với mã nguồn AI cung cấp. Bổ sung thêm logic tự động lưu mã giao dịch tạm thời (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>vnp_TxnRef</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) vào bảng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>appointments</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> với trạng thái </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>PENDING_PAYMENT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trước khi redirect khách hàng sang VNPAY để dễ dàng đối soát.</t>
+    </r>
+  </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>Xử lý các lịch hẹn bị treo hoặc khách hàng không hoàn tất thanh toán trên cổng VNPAY (quá thời gian giữ chỗ).</t>
+  </si>
+  <si>
+    <t>"Đề xuất giải pháp xử lý tự động các lịch hẹn có trạng thái PENDING_PAYMENT quá 15 phút mà không nhận được phản hồi IPN từ VNPAY để giải phóng slot cho khách hàng khác."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gợi ý tạo một cron job chạy định kỳ mỗi 5 phút quét cơ sở dữ liệu và cập nhật các lịch hẹn hết hạn thành </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>CANCELLED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nhận thấy giải pháp cron job hợp lý. Áp dụng thư viện </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>@nestjs/schedule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để triển khai, đồng thời tích hợp thêm bước hoàn trả số lượng đặt lịch song song (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>max_parallel_bookings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) của chi nhánh đó về lại trạng thái ban đầu để tránh bị giữ slot ảo.</t>
+    </r>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Xác thực tính toàn vẹn dữ liệu của webhook (IPN URL) từ VNPAY gửi về hệ thống AuraSpa nhằm tránh việc người dùng giả mạo kết quả thanh toán.</t>
+  </si>
+  <si>
+    <t>"Viết hàm verifyVnpaySignature trong NestJS để kiểm tra tính hợp lệ của mã kiểm tra (vnp_SecureHash) nhận được từ VNPAY IPN so với chuỗi hash tự tính toán."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI hướng dẫn cách lọc bỏ tham số hash, sắp xếp các tham số còn lại chuỗi query và dùng module </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>crypto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để tính toán lại mã HMAC-SHA512 nhằm đối chiếu đối lập.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Áp dụng chuẩn mã nguồn của AI. Bổ sung thêm bước kiểm tra nghiêm ngặt số tiền thanh toán (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>vnp_Amount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) và trạng thái giao dịch hiện tại trong database để tránh trường hợp tấn công replay (IPN giả mạo).</t>
+    </r>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>Gửi email tự động thông báo xác nhận đặt lịch thành công kèm mã QR check-in cho khách hàng sau khi thanh toán thành công.</t>
+  </si>
+  <si>
+    <t>"Hướng dẫn cấu hình Nodemailer với Gmail OAuth2 trong NestJS và viết service gửi email định dạng HTML template kèm file đính kèm là ảnh QR Code."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cung cấp cách cài đặt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>@nestjs-modules/mailer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, cấu hình thông số OAuth2 và hàm gửi mail dùng Handlebars template.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tận dụng giải pháp Handlebars để thiết kế template email của AuraSpa. Chỉnh sửa phần sinh QR Code bằng thư viện </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>qrcode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> dạng base64 rồi nhúng trực tiếp dưới dạng CID attachment vào email để đảm bảo hiển thị tốt trên mọi trình duyệt mail.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,6 +787,18 @@
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1075,126 +1401,43 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
-      <c r="A2" s="16">
-        <v>8</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="56">
-      <c r="A3" s="16">
-        <v>9</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="56">
-      <c r="A4" s="16">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="70">
-      <c r="A5" s="16">
-        <v>11</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>65</v>
-      </c>
+    <row r="2" spans="1:12">
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0A2B67-D23B-4DD4-996A-E5076823F00F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1240,7 +1483,7 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="70">
+    <row r="2" spans="1:12" ht="56">
       <c r="A2" s="17">
         <v>4</v>
       </c>
@@ -1263,7 +1506,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="70">
+    <row r="3" spans="1:12" ht="56">
       <c r="A3" s="17">
         <v>5</v>
       </c>
@@ -1309,7 +1552,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="84">
+    <row r="5" spans="1:12" ht="70">
       <c r="A5" s="17">
         <v>7</v>
       </c>
@@ -1654,96 +1897,96 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
+    <row r="2" spans="1:12" ht="70">
       <c r="A2" s="16">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="56">
       <c r="A3" s="16">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="56">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="70">
       <c r="A4" s="16">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="70">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="56">
       <c r="A5" s="16">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1769,19 +2012,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>4</v>
@@ -1792,100 +2035,101 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
+    <row r="2" spans="1:12" ht="70">
       <c r="A2" s="16">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="70">
+      <c r="A3" s="16">
+        <v>21</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="56">
-      <c r="A3" s="16">
-        <v>9</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>7</v>
-      </c>
       <c r="C3" s="17" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="56">
       <c r="A4" s="16">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="70">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="56">
       <c r="A5" s="16">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1930,97 +2174,41 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
-      <c r="A2" s="16">
-        <v>8</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="56">
-      <c r="A3" s="16">
-        <v>9</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="56">
-      <c r="A4" s="16">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="70">
-      <c r="A5" s="16">
-        <v>11</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>65</v>
-      </c>
+    <row r="2" spans="1:12">
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2068,97 +2256,41 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
-      <c r="A2" s="16">
-        <v>8</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="56">
-      <c r="A3" s="16">
-        <v>9</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="56">
-      <c r="A4" s="16">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="70">
-      <c r="A5" s="16">
-        <v>11</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>65</v>
-      </c>
+    <row r="2" spans="1:12">
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2206,97 +2338,41 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
-      <c r="A2" s="16">
-        <v>8</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="56">
-      <c r="A3" s="16">
-        <v>9</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="56">
-      <c r="A4" s="16">
-        <v>10</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="70">
-      <c r="A5" s="16">
-        <v>11</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>65</v>
-      </c>
+    <row r="2" spans="1:12">
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AI Audit Log_LeVanDai.xlsx
+++ b/AI Audit Log_LeVanDai.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/917556b196d2d829/Desktop/SWP391/ai-audit-log-LeVanDaiDE290256/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{ED16BCF0-CF13-415F-AF1E-AE119F2C1B37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{30F8FB22-79E7-428E-ABEF-D084E9CEC40F}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{ED16BCF0-CF13-415F-AF1E-AE119F2C1B37}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{1705B4F4-B604-430F-AA6C-D6ED2BFF852D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="9" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="142">
   <si>
     <t>STT</t>
   </si>
@@ -722,6 +722,331 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> dạng base64 rồi nhúng trực tiếp dưới dạng CID attachment vào email để đảm bảo hiển thị tốt trên mọi trình duyệt mail.</t>
+    </r>
+  </si>
+  <si>
+    <t>Decomposition</t>
+  </si>
+  <si>
+    <t>Thiết kế module Quản lý Phân quyền bảo mật (RBAC) cho 5 roles: Owner, Manager, Staff, Customer, Guest.</t>
+  </si>
+  <si>
+    <t>"Xây dựng cấu trúc Roles Guard và Custom Decorator trong NestJS sử dụng Passport JWT để kiểm tra và phân quyền truy cập cho API hệ thống Spa."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI cung cấp mã nguồn tạo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>RolesGuard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> kết hợp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>Reflector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để đọc metadata từ endpoint và so sánh với trường </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>role</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trong payload của JWT Token.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sơn đã áp dụng Guard này vào các controller </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>/branches</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>/services</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Giúp bảo vệ API, chỉ cho phép Owner/Manager chỉnh sửa thông tin, còn Customer chỉ được xem.</t>
+    </r>
+  </si>
+  <si>
+    <t>Rà soát lỗi bảo mật hệ thống khi lưu mật khẩu người dùng dưới dạng bản rõ trong cơ sở dữ liệu.</t>
+  </si>
+  <si>
+    <t>"Cách tích hợp thư viện bcryptjs vào module Auth của NestJS để hash mật khẩu tự động trước khi lưu vào PostgreSQL thông qua TypeORM Subscriber."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI hướng dẫn cách sử dụng hook </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>@BeforeInsert()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trong Entity của TypeORM để tự động hash password bằng hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>bcrypt.hash()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> với salt round là 10.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đại đã triển khai logic này vào </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>UserEntity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Đảm bảo dữ liệu mật khẩu của khách hàng luôn được mã hóa an toàn, không bị rò rỉ kể cả khi DB bị tấn công.</t>
+    </r>
+  </si>
+  <si>
+    <t>Research Stage</t>
+  </si>
+  <si>
+    <t>Lựa chọn giải pháp xử lý bất đồng bộ khi gửi Email xác nhận đặt lịch tự động cho khách hàng để không làm nghẽn luồng xử lý API chính.</t>
+  </si>
+  <si>
+    <t>"So sánh việc dùng BullMQ (Redis-based queue) và việc xử lý bất đồng bộ thông thường trong NestJS cho tính năng gửi Email OTP và thông báo đặt lịch."</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI phân tích và khuyên dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>BullMQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> vì giúp tách biệt tác vụ nặng (gửi mail) ra khỏi main thread, hỗ trợ cơ chế retry tự động nếu dịch vụ Mail server lỗi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nhóm quyết định cài đặt thêm Redis làm Message Queue. Thông đã viết </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>AudioProcessor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để xử lý hàng đợi gửi mail, giúp API đặt lịch phản hồi cho khách hàng chỉ dưới 200ms.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xử lý bài toán Overbooking (Trùng lịch): Không cho phép đặt lịch tại một chi nhánh nếu khung giờ đó đã đạt tối đa số ca phục vụ song song.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Viết câu truy vấn TypeORM kiểm tra tổng số lịch hẹn hiện tại của một chi nhánh dựa trên thuộc tính </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>max_parallel_bookings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trước khi cho phép tạo lịch mới."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI gợi ý sử dụng cơ chế </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>QueryRunner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để thiết lập Database Transaction, dùng lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>SELECT ... FOR UPDATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> để lock dòng dữ liệu, tránh tình trạng Race Condition.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Minh và Sơn đã áp dụng Transaction vào </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>AppointmentService</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Nhờ vậy, hệ thống chặn đứng lỗi đặt trùng lịch khi nhiều khách hàng cùng bấm đặt một khung giờ tại một chi nhánh.</t>
     </r>
   </si>
 </sst>
@@ -729,7 +1054,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -798,6 +1123,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1237,18 +1569,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" customWidth="1"/>
-    <col min="2" max="2" width="32.08203125" customWidth="1"/>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="2" max="2" width="32.125" customWidth="1"/>
     <col min="3" max="3" width="40.5" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.875" customWidth="1"/>
     <col min="5" max="5" width="24.25" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
-    <col min="7" max="7" width="55.6640625" customWidth="1"/>
+    <col min="7" max="7" width="55.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="56">
+    <row r="1" spans="1:10" ht="59.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1300,7 +1632,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" ht="84">
+    <row r="3" spans="1:10" ht="85.5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1326,7 +1658,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="70">
+    <row r="4" spans="1:10" ht="71.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1363,17 +1695,17 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E016D57F-1E9A-46C6-A9D7-2EF9F505177F}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1445,17 +1777,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="59.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1483,7 +1815,7 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
+    <row r="2" spans="1:12" ht="57">
       <c r="A2" s="17">
         <v>4</v>
       </c>
@@ -1506,7 +1838,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="56">
+    <row r="3" spans="1:12" ht="71.25">
       <c r="A3" s="17">
         <v>5</v>
       </c>
@@ -1529,7 +1861,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="56">
+    <row r="4" spans="1:12" ht="57">
       <c r="A4" s="17">
         <v>6</v>
       </c>
@@ -1552,7 +1884,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="70">
+    <row r="5" spans="1:12" ht="85.5">
       <c r="A5" s="17">
         <v>7</v>
       </c>
@@ -1583,17 +1915,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0484857C-4A21-4A6B-B466-F18AAC78F0ED}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1621,7 +1953,7 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
+    <row r="2" spans="1:12" ht="57">
       <c r="A2" s="16">
         <v>8</v>
       </c>
@@ -1644,7 +1976,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="56">
+    <row r="3" spans="1:12" ht="57">
       <c r="A3" s="16">
         <v>9</v>
       </c>
@@ -1667,7 +1999,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="56">
+    <row r="4" spans="1:12" ht="57">
       <c r="A4" s="16">
         <v>10</v>
       </c>
@@ -1690,7 +2022,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="70">
+    <row r="5" spans="1:12" ht="71.25">
       <c r="A5" s="16">
         <v>11</v>
       </c>
@@ -1721,17 +2053,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC6560E-89F1-42E8-87A4-F335DF5D1C50}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1759,7 +2091,7 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="56">
+    <row r="2" spans="1:12" ht="57">
       <c r="A2" s="16">
         <v>12</v>
       </c>
@@ -1782,7 +2114,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="56">
+    <row r="3" spans="1:12" ht="57">
       <c r="A3" s="16">
         <v>13</v>
       </c>
@@ -1805,7 +2137,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="56">
+    <row r="4" spans="1:12" ht="57">
       <c r="A4" s="16">
         <v>14</v>
       </c>
@@ -1828,7 +2160,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="56">
+    <row r="5" spans="1:12" ht="57">
       <c r="A5" s="16">
         <v>15</v>
       </c>
@@ -1859,17 +2191,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29DC8F4C-1351-4FE4-8122-15F34B9A48D6}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1897,7 +2229,7 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="70">
+    <row r="2" spans="1:12" ht="71.25">
       <c r="A2" s="16">
         <v>16</v>
       </c>
@@ -1920,7 +2252,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="56">
+    <row r="3" spans="1:12" ht="57">
       <c r="A3" s="16">
         <v>17</v>
       </c>
@@ -1943,7 +2275,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="70">
+    <row r="4" spans="1:12" ht="71.25">
       <c r="A4" s="16">
         <v>18</v>
       </c>
@@ -1966,7 +2298,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="56">
+    <row r="5" spans="1:12" ht="57">
       <c r="A5" s="16">
         <v>19</v>
       </c>
@@ -1997,17 +2329,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFCC2499-BED8-4AA5-94CB-7C8751FC2540}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2035,7 +2367,7 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" spans="1:12" ht="70">
+    <row r="2" spans="1:12" ht="71.25">
       <c r="A2" s="16">
         <v>20</v>
       </c>
@@ -2058,7 +2390,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="70">
+    <row r="3" spans="1:12" ht="71.25">
       <c r="A3" s="16">
         <v>21</v>
       </c>
@@ -2081,7 +2413,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="56">
+    <row r="4" spans="1:12" ht="57">
       <c r="A4" s="16">
         <v>22</v>
       </c>
@@ -2104,7 +2436,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="56">
+    <row r="5" spans="1:12" ht="57">
       <c r="A5" s="16">
         <v>23</v>
       </c>
@@ -2136,17 +2468,156 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E18554F2-18D8-43A5-949D-1BC2080C9515}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="70.5" customHeight="1">
+      <c r="A2" s="16">
+        <v>24</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="72.75" customHeight="1">
+      <c r="A3" s="16">
+        <v>25</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="64.5" customHeight="1">
+      <c r="A4" s="16">
+        <v>26</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="57">
+      <c r="A5" s="16">
+        <v>27</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A587915-313D-45B6-93D4-397D77ADF393}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
+    <col min="6" max="6" width="43.25" customWidth="1"/>
+    <col min="7" max="7" width="59" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2215,20 +2686,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A587915-313D-45B6-93D4-397D77ADF393}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{735CF029-11BF-4654-9E3E-B740C3374434}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
+    <col min="2" max="2" width="31.375" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
+    <col min="4" max="4" width="44.125" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
     <col min="6" max="6" width="43.25" customWidth="1"/>
     <col min="7" max="7" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
+    <row r="1" spans="1:12" ht="57.6" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2295,86 +2766,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{735CF029-11BF-4654-9E3E-B740C3374434}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="2" max="2" width="31.4140625" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="44.1640625" customWidth="1"/>
-    <col min="5" max="5" width="38.4140625" customWidth="1"/>
-    <col min="6" max="6" width="43.25" customWidth="1"/>
-    <col min="7" max="7" width="59" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="57.5" customHeight="1">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="16"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>